--- a/output/pdf_financials_xlsx/PBF.xlsx
+++ b/output/pdf_financials_xlsx/PBF.xlsx
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.082719</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.055054</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001543</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.00143</v>
       </c>
     </row>
     <row r="35">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.082719</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.055054</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001543</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.00143</v>
       </c>
     </row>
     <row r="37">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.514787</v>
+        <v>0.432068</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.240888</v>
+        <v>0.185834</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004101</v>
+        <v>0.002558</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">

--- a/output/pdf_financials_xlsx/PBF.xlsx
+++ b/output/pdf_financials_xlsx/PBF.xlsx
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.247487</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.017548</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.004709</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0.037161</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.252196</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.037161</v>
+        <v>0.054709</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.017275</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.432068</v>
+        <v>0.179872</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.185834</v>
+        <v>0.168286</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.002558</v>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.080665</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.080665</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-3.654875</v>
+        <v>-3.73554</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-1.838518</v>
@@ -5190,7 +5190,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -7078,7 +7082,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E111" s="5" t="n">
         <v>-0.080665</v>
       </c>
